--- a/ONT-SA/original/historical_sa_recipients_dataset_en.xlsx
+++ b/ONT-SA/original/historical_sa_recipients_dataset_en.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10914"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{337BBEE7-EBD7-4F54-B32C-13AE3F6122E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-11562" yWindow="6384" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="6380" windowWidth="23240" windowHeight="13880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Monthly" sheetId="1" r:id="rId1"/>
@@ -52,8 +52,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -107,11 +107,11 @@
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -124,19 +124,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -452,13 +452,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D3318"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="1"/>
-    <col min="2" max="2" width="10.77734375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.77734375" style="4" customWidth="1"/>
-    <col min="4" max="4" width="12.44140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="8.85546875" style="1"/>
+    <col min="2" max="2" width="10.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
@@ -643,7 +643,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>1970</v>
       </c>
@@ -657,7 +657,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>1970</v>
       </c>
@@ -671,7 +671,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>1970</v>
       </c>
@@ -685,7 +685,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>1970</v>
       </c>
@@ -699,7 +699,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>1970</v>
       </c>
@@ -713,7 +713,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>1970</v>
       </c>
@@ -727,7 +727,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>1970</v>
       </c>
@@ -741,7 +741,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>1970</v>
       </c>
@@ -755,7 +755,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>1970</v>
       </c>
@@ -769,7 +769,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>1970</v>
       </c>
@@ -783,7 +783,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>1970</v>
       </c>
@@ -797,7 +797,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>1970</v>
       </c>
@@ -979,7 +979,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <v>1972</v>
       </c>
@@ -993,7 +993,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <v>1972</v>
       </c>
@@ -1007,7 +1007,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
         <v>1972</v>
       </c>
@@ -1021,7 +1021,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <v>1972</v>
       </c>
@@ -1035,7 +1035,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
         <v>1972</v>
       </c>
@@ -1049,7 +1049,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
         <v>1972</v>
       </c>
@@ -1063,7 +1063,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
         <v>1972</v>
       </c>
@@ -1077,7 +1077,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
         <v>1972</v>
       </c>
@@ -1091,7 +1091,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
         <v>1972</v>
       </c>
@@ -1105,7 +1105,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="47" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
         <v>1972</v>
       </c>
@@ -1119,7 +1119,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="48" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
         <v>1972</v>
       </c>
@@ -1133,7 +1133,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="49" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
         <v>1972</v>
       </c>
@@ -1315,7 +1315,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="62" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
         <v>1974</v>
       </c>
@@ -1329,7 +1329,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="63" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
         <v>1974</v>
       </c>
@@ -1343,7 +1343,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="64" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
         <v>1974</v>
       </c>
@@ -1357,7 +1357,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="65" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
         <v>1974</v>
       </c>
@@ -1371,7 +1371,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="66" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
         <v>1974</v>
       </c>
@@ -1385,7 +1385,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="67" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
         <v>1974</v>
       </c>
@@ -1399,7 +1399,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="68" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
         <v>1974</v>
       </c>
@@ -1413,7 +1413,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="69" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
         <v>1974</v>
       </c>
@@ -1427,7 +1427,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="70" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
         <v>1974</v>
       </c>
@@ -1441,7 +1441,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="71" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A71" s="2">
         <v>1974</v>
       </c>
@@ -1455,7 +1455,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="72" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A72" s="2">
         <v>1974</v>
       </c>
@@ -1469,7 +1469,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="73" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A73" s="2">
         <v>1974</v>
       </c>
@@ -1651,7 +1651,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="86" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A86" s="2">
         <v>1976</v>
       </c>
@@ -1665,7 +1665,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="87" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A87" s="2">
         <v>1976</v>
       </c>
@@ -1679,7 +1679,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="88" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A88" s="2">
         <v>1976</v>
       </c>
@@ -1693,7 +1693,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="89" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A89" s="2">
         <v>1976</v>
       </c>
@@ -1707,7 +1707,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A90" s="2">
         <v>1976</v>
       </c>
@@ -1721,7 +1721,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="91" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A91" s="2">
         <v>1976</v>
       </c>
@@ -1735,7 +1735,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="92" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A92" s="2">
         <v>1976</v>
       </c>
@@ -1749,7 +1749,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="93" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A93" s="2">
         <v>1976</v>
       </c>
@@ -1763,7 +1763,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="94" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A94" s="2">
         <v>1976</v>
       </c>
@@ -1777,7 +1777,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="95" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A95" s="2">
         <v>1976</v>
       </c>
@@ -1791,7 +1791,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="96" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A96" s="2">
         <v>1976</v>
       </c>
@@ -1805,7 +1805,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="97" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A97" s="2">
         <v>1976</v>
       </c>
@@ -1987,7 +1987,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="110" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A110" s="2">
         <v>1978</v>
       </c>
@@ -2001,7 +2001,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="111" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A111" s="2">
         <v>1978</v>
       </c>
@@ -2015,7 +2015,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="112" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A112" s="2">
         <v>1978</v>
       </c>
@@ -2029,7 +2029,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="113" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A113" s="2">
         <v>1978</v>
       </c>
@@ -2043,7 +2043,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="114" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A114" s="2">
         <v>1978</v>
       </c>
@@ -2057,7 +2057,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="115" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A115" s="2">
         <v>1978</v>
       </c>
@@ -2071,7 +2071,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="116" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A116" s="2">
         <v>1978</v>
       </c>
@@ -2085,7 +2085,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="117" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A117" s="2">
         <v>1978</v>
       </c>
@@ -2099,7 +2099,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="118" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A118" s="2">
         <v>1978</v>
       </c>
@@ -2113,7 +2113,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="119" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A119" s="2">
         <v>1978</v>
       </c>
@@ -2127,7 +2127,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="120" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A120" s="2">
         <v>1978</v>
       </c>
@@ -2141,7 +2141,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="121" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A121" s="2">
         <v>1978</v>
       </c>
@@ -2323,7 +2323,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="134" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A134" s="2">
         <v>1980</v>
       </c>
@@ -2337,7 +2337,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="135" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A135" s="2">
         <v>1980</v>
       </c>
@@ -2351,7 +2351,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="136" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A136" s="2">
         <v>1980</v>
       </c>
@@ -2365,7 +2365,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="137" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A137" s="2">
         <v>1980</v>
       </c>
@@ -2379,7 +2379,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="138" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A138" s="2">
         <v>1980</v>
       </c>
@@ -2393,7 +2393,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="139" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A139" s="2">
         <v>1980</v>
       </c>
@@ -2407,7 +2407,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="140" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A140" s="2">
         <v>1980</v>
       </c>
@@ -2421,7 +2421,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="141" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A141" s="2">
         <v>1980</v>
       </c>
@@ -2435,7 +2435,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="142" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A142" s="2">
         <v>1980</v>
       </c>
@@ -2449,7 +2449,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="143" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A143" s="2">
         <v>1980</v>
       </c>
@@ -2463,7 +2463,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="144" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A144" s="2">
         <v>1980</v>
       </c>
@@ -2477,7 +2477,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="145" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A145" s="2">
         <v>1980</v>
       </c>
@@ -2659,7 +2659,7 @@
         <v>392539.68855370698</v>
       </c>
     </row>
-    <row r="158" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A158" s="2">
         <v>1982</v>
       </c>
@@ -2673,7 +2673,7 @@
         <v>402682.84195413551</v>
       </c>
     </row>
-    <row r="159" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A159" s="2">
         <v>1982</v>
       </c>
@@ -2687,7 +2687,7 @@
         <v>407781.67678630538</v>
       </c>
     </row>
-    <row r="160" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A160" s="2">
         <v>1982</v>
       </c>
@@ -2701,7 +2701,7 @@
         <v>414684.90428423078</v>
       </c>
     </row>
-    <row r="161" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A161" s="2">
         <v>1982</v>
       </c>
@@ -2715,7 +2715,7 @@
         <v>409314.45324508502</v>
       </c>
     </row>
-    <row r="162" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A162" s="2">
         <v>1982</v>
       </c>
@@ -2729,7 +2729,7 @@
         <v>404282.73998380359</v>
       </c>
     </row>
-    <row r="163" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A163" s="2">
         <v>1982</v>
       </c>
@@ -2743,7 +2743,7 @@
         <v>401920.06777877803</v>
       </c>
     </row>
-    <row r="164" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A164" s="2">
         <v>1982</v>
       </c>
@@ -2757,7 +2757,7 @@
         <v>400748.1037513928</v>
       </c>
     </row>
-    <row r="165" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A165" s="2">
         <v>1982</v>
       </c>
@@ -2771,7 +2771,7 @@
         <v>402968.15345083294</v>
       </c>
     </row>
-    <row r="166" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A166" s="2">
         <v>1982</v>
       </c>
@@ -2785,7 +2785,7 @@
         <v>412746.15785589931</v>
       </c>
     </row>
-    <row r="167" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A167" s="2">
         <v>1982</v>
       </c>
@@ -2799,7 +2799,7 @@
         <v>419831.44814672775</v>
       </c>
     </row>
-    <row r="168" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A168" s="2">
         <v>1982</v>
       </c>
@@ -2813,7 +2813,7 @@
         <v>435408.85828514391</v>
       </c>
     </row>
-    <row r="169" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A169" s="2">
         <v>1982</v>
       </c>
@@ -2995,7 +2995,7 @@
         <v>465750.21555223246</v>
       </c>
     </row>
-    <row r="182" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A182" s="2">
         <v>1984</v>
       </c>
@@ -3009,7 +3009,7 @@
         <v>481942.12265494914</v>
       </c>
     </row>
-    <row r="183" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A183" s="2">
         <v>1984</v>
       </c>
@@ -3023,7 +3023,7 @@
         <v>487997.5686173198</v>
       </c>
     </row>
-    <row r="184" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A184" s="2">
         <v>1984</v>
       </c>
@@ -3037,7 +3037,7 @@
         <v>488192.76807002159</v>
       </c>
     </row>
-    <row r="185" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A185" s="2">
         <v>1984</v>
       </c>
@@ -3051,7 +3051,7 @@
         <v>481333.52854849992</v>
       </c>
     </row>
-    <row r="186" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A186" s="2">
         <v>1984</v>
       </c>
@@ -3065,7 +3065,7 @@
         <v>478143.33899419761</v>
       </c>
     </row>
-    <row r="187" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A187" s="2">
         <v>1984</v>
       </c>
@@ -3079,7 +3079,7 @@
         <v>467219.86322050582</v>
       </c>
     </row>
-    <row r="188" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A188" s="2">
         <v>1984</v>
       </c>
@@ -3093,7 +3093,7 @@
         <v>462124.65494300716</v>
       </c>
     </row>
-    <row r="189" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A189" s="2">
         <v>1984</v>
       </c>
@@ -3107,7 +3107,7 @@
         <v>460968.30771505123</v>
       </c>
     </row>
-    <row r="190" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A190" s="2">
         <v>1984</v>
       </c>
@@ -3121,7 +3121,7 @@
         <v>459650.46128441067</v>
       </c>
     </row>
-    <row r="191" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A191" s="2">
         <v>1984</v>
       </c>
@@ -3135,7 +3135,7 @@
         <v>462952.25309149292</v>
       </c>
     </row>
-    <row r="192" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A192" s="2">
         <v>1984</v>
       </c>
@@ -3149,7 +3149,7 @@
         <v>469335.49409477663</v>
       </c>
     </row>
-    <row r="193" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A193" s="2">
         <v>1984</v>
       </c>
@@ -3331,7 +3331,7 @@
         <v>477014.86738039739</v>
       </c>
     </row>
-    <row r="206" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A206" s="2">
         <v>1986</v>
       </c>
@@ -3345,7 +3345,7 @@
         <v>492047.03812880488</v>
       </c>
     </row>
-    <row r="207" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A207" s="2">
         <v>1986</v>
       </c>
@@ -3359,7 +3359,7 @@
         <v>490794.56051857199</v>
       </c>
     </row>
-    <row r="208" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A208" s="2">
         <v>1986</v>
       </c>
@@ -3373,7 +3373,7 @@
         <v>488200.21417655447</v>
       </c>
     </row>
-    <row r="209" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A209" s="2">
         <v>1986</v>
       </c>
@@ -3387,7 +3387,7 @@
         <v>489545.47180520277</v>
       </c>
     </row>
-    <row r="210" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A210" s="2">
         <v>1986</v>
       </c>
@@ -3401,7 +3401,7 @@
         <v>484288.06097910111</v>
       </c>
     </row>
-    <row r="211" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A211" s="2">
         <v>1986</v>
       </c>
@@ -3415,7 +3415,7 @@
         <v>479613.11415415525</v>
       </c>
     </row>
-    <row r="212" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A212" s="2">
         <v>1986</v>
       </c>
@@ -3429,7 +3429,7 @@
         <v>479471.62311254279</v>
       </c>
     </row>
-    <row r="213" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A213" s="2">
         <v>1986</v>
       </c>
@@ -3443,7 +3443,7 @@
         <v>476062.20964235195</v>
       </c>
     </row>
-    <row r="214" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A214" s="2">
         <v>1986</v>
       </c>
@@ -3457,7 +3457,7 @@
         <v>480185.24732772022</v>
       </c>
     </row>
-    <row r="215" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A215" s="2">
         <v>1986</v>
       </c>
@@ -3471,7 +3471,7 @@
         <v>483539.33293191018</v>
       </c>
     </row>
-    <row r="216" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A216" s="2">
         <v>1986</v>
       </c>
@@ -3485,7 +3485,7 @@
         <v>489171.89217675629</v>
       </c>
     </row>
-    <row r="217" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A217" s="2">
         <v>1986</v>
       </c>
@@ -3667,7 +3667,7 @@
         <v>517329.31074003794</v>
       </c>
     </row>
-    <row r="230" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A230" s="2">
         <v>1988</v>
       </c>
@@ -3681,7 +3681,7 @@
         <v>527679.43037338415</v>
       </c>
     </row>
-    <row r="231" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A231" s="2">
         <v>1988</v>
       </c>
@@ -3695,7 +3695,7 @@
         <v>534309.94145407481</v>
       </c>
     </row>
-    <row r="232" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A232" s="2">
         <v>1988</v>
       </c>
@@ -3709,7 +3709,7 @@
         <v>532925.61267002753</v>
       </c>
     </row>
-    <row r="233" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A233" s="2">
         <v>1988</v>
       </c>
@@ -3723,7 +3723,7 @@
         <v>532487.1500662769</v>
       </c>
     </row>
-    <row r="234" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A234" s="2">
         <v>1988</v>
       </c>
@@ -3737,7 +3737,7 @@
         <v>528112.61023250944</v>
       </c>
     </row>
-    <row r="235" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A235" s="2">
         <v>1988</v>
       </c>
@@ -3751,7 +3751,7 @@
         <v>526030.83974685322</v>
       </c>
     </row>
-    <row r="236" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A236" s="2">
         <v>1988</v>
       </c>
@@ -3765,7 +3765,7 @@
         <v>519101.55525423726</v>
       </c>
     </row>
-    <row r="237" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A237" s="2">
         <v>1988</v>
       </c>
@@ -3779,7 +3779,7 @@
         <v>525645.75565493316</v>
       </c>
     </row>
-    <row r="238" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A238" s="2">
         <v>1988</v>
       </c>
@@ -3793,7 +3793,7 @@
         <v>530580.98144714232</v>
       </c>
     </row>
-    <row r="239" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A239" s="2">
         <v>1988</v>
       </c>
@@ -3807,7 +3807,7 @@
         <v>535050.55144450557</v>
       </c>
     </row>
-    <row r="240" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A240" s="2">
         <v>1988</v>
       </c>
@@ -3821,7 +3821,7 @@
         <v>545426.83498542267</v>
       </c>
     </row>
-    <row r="241" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A241" s="2">
         <v>1988</v>
       </c>
@@ -4003,7 +4003,7 @@
         <v>606710.32751950272</v>
       </c>
     </row>
-    <row r="254" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A254" s="2">
         <v>1990</v>
       </c>
@@ -4017,7 +4017,7 @@
         <v>636744.85899798421</v>
       </c>
     </row>
-    <row r="255" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A255" s="2">
         <v>1990</v>
       </c>
@@ -4031,7 +4031,7 @@
         <v>647067.59563292027</v>
       </c>
     </row>
-    <row r="256" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A256" s="2">
         <v>1990</v>
       </c>
@@ -4045,7 +4045,7 @@
         <v>663137.60884203925</v>
       </c>
     </row>
-    <row r="257" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A257" s="2">
         <v>1990</v>
       </c>
@@ -4059,7 +4059,7 @@
         <v>666698.31073170737</v>
       </c>
     </row>
-    <row r="258" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A258" s="2">
         <v>1990</v>
       </c>
@@ -4073,7 +4073,7 @@
         <v>679728.5359366776</v>
       </c>
     </row>
-    <row r="259" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A259" s="2">
         <v>1990</v>
       </c>
@@ -4087,7 +4087,7 @@
         <v>687480.30980969069</v>
       </c>
     </row>
-    <row r="260" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A260" s="2">
         <v>1990</v>
       </c>
@@ -4101,7 +4101,7 @@
         <v>696285.88928568945</v>
       </c>
     </row>
-    <row r="261" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A261" s="2">
         <v>1990</v>
       </c>
@@ -4115,7 +4115,7 @@
         <v>715164.87866126234</v>
       </c>
     </row>
-    <row r="262" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A262" s="2">
         <v>1990</v>
       </c>
@@ -4129,7 +4129,7 @@
         <v>730859.15823200904</v>
       </c>
     </row>
-    <row r="263" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A263" s="2">
         <v>1990</v>
       </c>
@@ -4143,7 +4143,7 @@
         <v>752762.83273202577</v>
       </c>
     </row>
-    <row r="264" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A264" s="2">
         <v>1990</v>
       </c>
@@ -4157,7 +4157,7 @@
         <v>778269.91635934403</v>
       </c>
     </row>
-    <row r="265" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A265" s="2">
         <v>1990</v>
       </c>
@@ -4339,7 +4339,7 @@
         <v>1099326.1229600001</v>
       </c>
     </row>
-    <row r="278" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A278" s="2">
         <v>1992</v>
       </c>
@@ -4353,7 +4353,7 @@
         <v>1136605</v>
       </c>
     </row>
-    <row r="279" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A279" s="2">
         <v>1992</v>
       </c>
@@ -4367,7 +4367,7 @@
         <v>1153463</v>
       </c>
     </row>
-    <row r="280" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A280" s="2">
         <v>1992</v>
       </c>
@@ -4381,7 +4381,7 @@
         <v>1166661</v>
       </c>
     </row>
-    <row r="281" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A281" s="2">
         <v>1992</v>
       </c>
@@ -4395,7 +4395,7 @@
         <v>1171236</v>
       </c>
     </row>
-    <row r="282" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A282" s="2">
         <v>1992</v>
       </c>
@@ -4409,7 +4409,7 @@
         <v>1178518</v>
       </c>
     </row>
-    <row r="283" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A283" s="2">
         <v>1992</v>
       </c>
@@ -4423,7 +4423,7 @@
         <v>1186488</v>
       </c>
     </row>
-    <row r="284" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A284" s="2">
         <v>1992</v>
       </c>
@@ -4437,7 +4437,7 @@
         <v>1191874</v>
       </c>
     </row>
-    <row r="285" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A285" s="2">
         <v>1992</v>
       </c>
@@ -4451,7 +4451,7 @@
         <v>1195347</v>
       </c>
     </row>
-    <row r="286" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A286" s="2">
         <v>1992</v>
       </c>
@@ -4465,7 +4465,7 @@
         <v>1206951</v>
       </c>
     </row>
-    <row r="287" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A287" s="2">
         <v>1992</v>
       </c>
@@ -4479,7 +4479,7 @@
         <v>1213397</v>
       </c>
     </row>
-    <row r="288" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A288" s="2">
         <v>1992</v>
       </c>
@@ -4493,7 +4493,7 @@
         <v>1227073</v>
       </c>
     </row>
-    <row r="289" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A289" s="2">
         <v>1992</v>
       </c>
@@ -4675,7 +4675,7 @@
         <v>1329760</v>
       </c>
     </row>
-    <row r="302" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A302" s="2">
         <v>1994</v>
       </c>
@@ -4689,7 +4689,7 @@
         <v>1341850</v>
       </c>
     </row>
-    <row r="303" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A303" s="2">
         <v>1994</v>
       </c>
@@ -4703,7 +4703,7 @@
         <v>1352015</v>
       </c>
     </row>
-    <row r="304" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A304" s="2">
         <v>1994</v>
       </c>
@@ -4717,7 +4717,7 @@
         <v>1362273</v>
       </c>
     </row>
-    <row r="305" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A305" s="2">
         <v>1994</v>
       </c>
@@ -4731,7 +4731,7 @@
         <v>1350302</v>
       </c>
     </row>
-    <row r="306" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A306" s="2">
         <v>1994</v>
       </c>
@@ -4745,7 +4745,7 @@
         <v>1348594</v>
       </c>
     </row>
-    <row r="307" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A307" s="2">
         <v>1994</v>
       </c>
@@ -4759,7 +4759,7 @@
         <v>1338340</v>
       </c>
     </row>
-    <row r="308" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A308" s="2">
         <v>1994</v>
       </c>
@@ -4773,7 +4773,7 @@
         <v>1322109</v>
       </c>
     </row>
-    <row r="309" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A309" s="2">
         <v>1994</v>
       </c>
@@ -4787,7 +4787,7 @@
         <v>1318208</v>
       </c>
     </row>
-    <row r="310" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A310" s="2">
         <v>1994</v>
       </c>
@@ -4801,7 +4801,7 @@
         <v>1310544</v>
       </c>
     </row>
-    <row r="311" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A311" s="2">
         <v>1994</v>
       </c>
@@ -4815,7 +4815,7 @@
         <v>1297365</v>
       </c>
     </row>
-    <row r="312" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A312" s="2">
         <v>1994</v>
       </c>
@@ -4829,7 +4829,7 @@
         <v>1301907</v>
       </c>
     </row>
-    <row r="313" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A313" s="2">
         <v>1994</v>
       </c>
@@ -5011,7 +5011,7 @@
         <v>1231928</v>
       </c>
     </row>
-    <row r="326" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A326" s="2">
         <v>1996</v>
       </c>
@@ -5025,7 +5025,7 @@
         <v>1225995</v>
       </c>
     </row>
-    <row r="327" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A327" s="2">
         <v>1996</v>
       </c>
@@ -5039,7 +5039,7 @@
         <v>1222402</v>
       </c>
     </row>
-    <row r="328" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A328" s="2">
         <v>1996</v>
       </c>
@@ -5053,7 +5053,7 @@
         <v>1216056</v>
       </c>
     </row>
-    <row r="329" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A329" s="2">
         <v>1996</v>
       </c>
@@ -5067,7 +5067,7 @@
         <v>1217883</v>
       </c>
     </row>
-    <row r="330" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A330" s="2">
         <v>1996</v>
       </c>
@@ -5081,7 +5081,7 @@
         <v>1222913</v>
       </c>
     </row>
-    <row r="331" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A331" s="2">
         <v>1996</v>
       </c>
@@ -5095,7 +5095,7 @@
         <v>1208622</v>
       </c>
     </row>
-    <row r="332" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A332" s="2">
         <v>1996</v>
       </c>
@@ -5109,7 +5109,7 @@
         <v>1197388</v>
       </c>
     </row>
-    <row r="333" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A333" s="2">
         <v>1996</v>
       </c>
@@ -5123,7 +5123,7 @@
         <v>1188918</v>
       </c>
     </row>
-    <row r="334" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A334" s="2">
         <v>1996</v>
       </c>
@@ -5137,7 +5137,7 @@
         <v>1165108</v>
       </c>
     </row>
-    <row r="335" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A335" s="2">
         <v>1996</v>
       </c>
@@ -5151,7 +5151,7 @@
         <v>1150878</v>
       </c>
     </row>
-    <row r="336" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A336" s="2">
         <v>1996</v>
       </c>
@@ -5165,7 +5165,7 @@
         <v>1144337</v>
       </c>
     </row>
-    <row r="337" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A337" s="2">
         <v>1996</v>
       </c>
@@ -5347,7 +5347,7 @@
         <v>1098659</v>
       </c>
     </row>
-    <row r="350" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A350" s="2">
         <v>1998</v>
       </c>
@@ -5361,7 +5361,7 @@
         <v>1099976</v>
       </c>
     </row>
-    <row r="351" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A351" s="2">
         <v>1998</v>
       </c>
@@ -5375,7 +5375,7 @@
         <v>1095300</v>
       </c>
     </row>
-    <row r="352" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A352" s="2">
         <v>1998</v>
       </c>
@@ -5389,7 +5389,7 @@
         <v>1091339</v>
       </c>
     </row>
-    <row r="353" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A353" s="2">
         <v>1998</v>
       </c>
@@ -5403,7 +5403,7 @@
         <v>1037416.5975</v>
       </c>
     </row>
-    <row r="354" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A354" s="2">
         <v>1998</v>
       </c>
@@ -5417,7 +5417,7 @@
         <v>1030401.9149</v>
       </c>
     </row>
-    <row r="355" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A355" s="2">
         <v>1998</v>
       </c>
@@ -5431,7 +5431,7 @@
         <v>1018838.6364</v>
       </c>
     </row>
-    <row r="356" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A356" s="2">
         <v>1998</v>
       </c>
@@ -5445,7 +5445,7 @@
         <v>1008124.1809</v>
       </c>
     </row>
-    <row r="357" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A357" s="2">
         <v>1998</v>
       </c>
@@ -5459,7 +5459,7 @@
         <v>998272.40110000002</v>
       </c>
     </row>
-    <row r="358" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A358" s="2">
         <v>1998</v>
       </c>
@@ -5473,7 +5473,7 @@
         <v>979180.86499999999</v>
       </c>
     </row>
-    <row r="359" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A359" s="2">
         <v>1998</v>
       </c>
@@ -5487,7 +5487,7 @@
         <v>962842.7435000001</v>
       </c>
     </row>
-    <row r="360" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A360" s="2">
         <v>1998</v>
       </c>
@@ -5501,7 +5501,7 @@
         <v>943779.7439</v>
       </c>
     </row>
-    <row r="361" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A361" s="2">
         <v>1998</v>
       </c>
@@ -5683,7 +5683,7 @@
         <v>837389.90809999988</v>
       </c>
     </row>
-    <row r="374" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A374" s="2">
         <v>2000</v>
       </c>
@@ -5697,7 +5697,7 @@
         <v>834269.65610000002</v>
       </c>
     </row>
-    <row r="375" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A375" s="2">
         <v>2000</v>
       </c>
@@ -5711,7 +5711,7 @@
         <v>826145.94090000005</v>
       </c>
     </row>
-    <row r="376" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A376" s="2">
         <v>2000</v>
       </c>
@@ -5725,7 +5725,7 @@
         <v>822739.1949</v>
       </c>
     </row>
-    <row r="377" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A377" s="2">
         <v>2000</v>
       </c>
@@ -5739,7 +5739,7 @@
         <v>810196.04190000007</v>
       </c>
     </row>
-    <row r="378" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A378" s="2">
         <v>2000</v>
       </c>
@@ -5753,7 +5753,7 @@
         <v>801323.45439999993</v>
       </c>
     </row>
-    <row r="379" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A379" s="2">
         <v>2000</v>
       </c>
@@ -5767,7 +5767,7 @@
         <v>794460.38670000003</v>
       </c>
     </row>
-    <row r="380" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A380" s="2">
         <v>2000</v>
       </c>
@@ -5781,7 +5781,7 @@
         <v>779369.7206</v>
       </c>
     </row>
-    <row r="381" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A381" s="2">
         <v>2000</v>
       </c>
@@ -5795,7 +5795,7 @@
         <v>773016.3848</v>
       </c>
     </row>
-    <row r="382" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A382" s="2">
         <v>2000</v>
       </c>
@@ -5809,7 +5809,7 @@
         <v>758955.62820000004</v>
       </c>
     </row>
-    <row r="383" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A383" s="2">
         <v>2000</v>
       </c>
@@ -5823,7 +5823,7 @@
         <v>742516.01280000003</v>
       </c>
     </row>
-    <row r="384" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A384" s="2">
         <v>2000</v>
       </c>
@@ -5837,7 +5837,7 @@
         <v>740188.32180000003</v>
       </c>
     </row>
-    <row r="385" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A385" s="2">
         <v>2000</v>
       </c>
@@ -6019,7 +6019,7 @@
         <v>706107.8075</v>
       </c>
     </row>
-    <row r="398" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A398" s="2">
         <v>2002</v>
       </c>
@@ -6033,7 +6033,7 @@
         <v>718488.37809999997</v>
       </c>
     </row>
-    <row r="399" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A399" s="2">
         <v>2002</v>
       </c>
@@ -6047,7 +6047,7 @@
         <v>716425.37880000006</v>
       </c>
     </row>
-    <row r="400" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A400" s="2">
         <v>2002</v>
       </c>
@@ -6061,7 +6061,7 @@
         <v>711862.98730000004</v>
       </c>
     </row>
-    <row r="401" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A401" s="2">
         <v>2002</v>
       </c>
@@ -6075,7 +6075,7 @@
         <v>710298.38419999997</v>
       </c>
     </row>
-    <row r="402" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A402" s="2">
         <v>2002</v>
       </c>
@@ -6089,7 +6089,7 @@
         <v>712344.71270000003</v>
       </c>
     </row>
-    <row r="403" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A403" s="2">
         <v>2002</v>
       </c>
@@ -6103,7 +6103,7 @@
         <v>710309.56660000002</v>
       </c>
     </row>
-    <row r="404" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A404" s="2">
         <v>2002</v>
       </c>
@@ -6117,7 +6117,7 @@
         <v>704904.69449999998</v>
       </c>
     </row>
-    <row r="405" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A405" s="2">
         <v>2002</v>
       </c>
@@ -6131,7 +6131,7 @@
         <v>704569.43900000001</v>
       </c>
     </row>
-    <row r="406" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A406" s="2">
         <v>2002</v>
       </c>
@@ -6145,7 +6145,7 @@
         <v>698893.31</v>
       </c>
     </row>
-    <row r="407" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A407" s="2">
         <v>2002</v>
       </c>
@@ -6159,7 +6159,7 @@
         <v>691122.63529999997</v>
       </c>
     </row>
-    <row r="408" spans="1:4" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:4" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A408" s="2">
         <v>2002</v>
       </c>
@@ -6173,7 +6173,7 @@
         <v>689107.62009999994</v>
       </c>
     </row>
-    <row r="409" spans="1:4" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A409" s="2">
         <v>2002</v>
       </c>
@@ -6355,7 +6355,7 @@
         <v>686229</v>
       </c>
     </row>
-    <row r="422" spans="1:4" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:4" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A422" s="2">
         <v>2004</v>
       </c>
@@ -6369,7 +6369,7 @@
         <v>693999</v>
       </c>
     </row>
-    <row r="423" spans="1:4" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:4" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A423" s="2">
         <v>2004</v>
       </c>
@@ -6383,7 +6383,7 @@
         <v>694895</v>
       </c>
     </row>
-    <row r="424" spans="1:4" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:4" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A424" s="2">
         <v>2004</v>
       </c>
@@ -6397,7 +6397,7 @@
         <v>698496</v>
       </c>
     </row>
-    <row r="425" spans="1:4" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:4" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A425" s="2">
         <v>2004</v>
       </c>
@@ -6411,7 +6411,7 @@
         <v>696936</v>
       </c>
     </row>
-    <row r="426" spans="1:4" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:4" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A426" s="2">
         <v>2004</v>
       </c>
@@ -6425,7 +6425,7 @@
         <v>696668</v>
       </c>
     </row>
-    <row r="427" spans="1:4" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:4" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A427" s="2">
         <v>2004</v>
       </c>
@@ -6439,7 +6439,7 @@
         <v>695977</v>
       </c>
     </row>
-    <row r="428" spans="1:4" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:4" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A428" s="2">
         <v>2004</v>
       </c>
@@ -6453,7 +6453,7 @@
         <v>692572</v>
       </c>
     </row>
-    <row r="429" spans="1:4" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:4" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A429" s="2">
         <v>2004</v>
       </c>
@@ -6467,7 +6467,7 @@
         <v>691655</v>
       </c>
     </row>
-    <row r="430" spans="1:4" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:4" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A430" s="2">
         <v>2004</v>
       </c>
@@ -6481,7 +6481,7 @@
         <v>690076</v>
       </c>
     </row>
-    <row r="431" spans="1:4" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:4" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A431" s="2">
         <v>2004</v>
       </c>
@@ -6495,7 +6495,7 @@
         <v>681343</v>
       </c>
     </row>
-    <row r="432" spans="1:4" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:4" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A432" s="2">
         <v>2004</v>
       </c>
@@ -6509,7 +6509,7 @@
         <v>681791</v>
       </c>
     </row>
-    <row r="433" spans="1:4" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:4" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A433" s="2">
         <v>2004</v>
       </c>
@@ -6691,7 +6691,7 @@
         <v>706198</v>
       </c>
     </row>
-    <row r="446" spans="1:4" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:4" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A446" s="2">
         <v>2006</v>
       </c>
@@ -6705,7 +6705,7 @@
         <v>713684</v>
       </c>
     </row>
-    <row r="447" spans="1:4" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:4" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A447" s="2">
         <v>2006</v>
       </c>
@@ -6719,7 +6719,7 @@
         <v>713672</v>
       </c>
     </row>
-    <row r="448" spans="1:4" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:4" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A448" s="2">
         <v>2006</v>
       </c>
@@ -6733,7 +6733,7 @@
         <v>717473</v>
       </c>
     </row>
-    <row r="449" spans="1:4" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:4" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A449" s="2">
         <v>2006</v>
       </c>
@@ -6747,7 +6747,7 @@
         <v>714837</v>
       </c>
     </row>
-    <row r="450" spans="1:4" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:4" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A450" s="2">
         <v>2006</v>
       </c>
@@ -6761,7 +6761,7 @@
         <v>718247</v>
       </c>
     </row>
-    <row r="451" spans="1:4" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:4" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A451" s="2">
         <v>2006</v>
       </c>
@@ -6775,7 +6775,7 @@
         <v>717967</v>
       </c>
     </row>
-    <row r="452" spans="1:4" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:4" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A452" s="2">
         <v>2006</v>
       </c>
@@ -6789,7 +6789,7 @@
         <v>715018</v>
       </c>
     </row>
-    <row r="453" spans="1:4" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:4" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A453" s="2">
         <v>2006</v>
       </c>
@@ -6803,7 +6803,7 @@
         <v>718707</v>
       </c>
     </row>
-    <row r="454" spans="1:4" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:4" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A454" s="2">
         <v>2006</v>
       </c>
@@ -6817,7 +6817,7 @@
         <v>716985</v>
       </c>
     </row>
-    <row r="455" spans="1:4" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:4" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A455" s="2">
         <v>2006</v>
       </c>
@@ -6831,7 +6831,7 @@
         <v>709851</v>
       </c>
     </row>
-    <row r="456" spans="1:4" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:4" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A456" s="2">
         <v>2006</v>
       </c>
@@ -6845,7 +6845,7 @@
         <v>713610</v>
       </c>
     </row>
-    <row r="457" spans="1:4" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:4" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A457" s="2">
         <v>2006</v>
       </c>
@@ -6859,7 +6859,7 @@
         <v>714814</v>
       </c>
     </row>
-    <row r="458" spans="1:4" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:4" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A458" s="2">
         <v>2007</v>
       </c>
